--- a/etf_holdings/2026-10-06_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:32</t>
+          <t>2026-10-06 01:24:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:32</t>
+          <t>2026-10-06 01:24:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:32</t>
+          <t>2026-10-06 01:24:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:33</t>
+          <t>2026-10-06 01:24:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:33</t>
+          <t>2026-10-06 01:24:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:33</t>
+          <t>2026-10-06 01:24:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:33</t>
+          <t>2026-10-06 01:24:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:33</t>
+          <t>2026-10-06 01:24:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:33</t>
+          <t>2026-10-06 01:24:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:35</t>
+          <t>2026-10-06 01:24:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:35</t>
+          <t>2026-10-06 01:24:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:35</t>
+          <t>2026-10-06 01:24:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:35</t>
+          <t>2026-10-06 01:24:40</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:35</t>
+          <t>2026-10-06 01:24:40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:35</t>
+          <t>2026-10-06 01:24:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/etf_holdings/2026-10-06_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:37</t>
+          <t>2026-10-06 02:28:07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:37</t>
+          <t>2026-10-06 02:28:07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:37</t>
+          <t>2026-10-06 02:28:07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:39</t>
+          <t>2026-10-06 02:28:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:39</t>
+          <t>2026-10-06 02:28:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:39</t>
+          <t>2026-10-06 02:28:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:39</t>
+          <t>2026-10-06 02:28:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:39</t>
+          <t>2026-10-06 02:28:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:39</t>
+          <t>2026-10-06 02:28:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:40</t>
+          <t>2026-10-06 02:28:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:40</t>
+          <t>2026-10-06 02:28:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:40</t>
+          <t>2026-10-06 02:28:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:40</t>
+          <t>2026-10-06 02:28:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:40</t>
+          <t>2026-10-06 02:28:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:40</t>
+          <t>2026-10-06 02:28:10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/etf_holdings/2026-10-06_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:07</t>
+          <t>2026-10-06 19:17:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,27 +509,27 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+6.37%2005</t>
+          <t>+2.24%2050</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+6.37%</t>
+          <t>+2.24%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.08%633,000</t>
+          <t>3.25%633,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.25%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:07</t>
+          <t>2026-10-06 19:17:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,27 +572,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+3%2575</t>
+          <t>+0.39%2585</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+3%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2575</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.62%406,000</t>
+          <t>2.68%406,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.68%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:07</t>
+          <t>2026-10-06 19:17:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,27 +635,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+1.53%1325</t>
+          <t>-1.13%1310</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.25%667,000</t>
+          <t>2.26%667,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -663,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:09</t>
+          <t>2026-10-06 19:17:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -698,27 +698,27 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+4.34%5165</t>
+          <t>-4.74%4920</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+4.34%</t>
+          <t>-4.74%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5165</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.11%165,000</t>
+          <t>2.18%165,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.18%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -726,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:09</t>
+          <t>2026-10-06 19:17:16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.08%103,200</t>
+          <t>2.15%103,200</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.15%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:09</t>
+          <t>2026-10-06 19:17:16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -819,40 +819,40 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6981MURATA MANUFACTURING CO LTD</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+5.18%5995</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+5.18%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5995</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.85%418,400</t>
+          <t>1.96%134,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>418400</v>
+        <v>134000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:09</t>
+          <t>2026-10-06 19:17:16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -882,40 +882,40 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>6981MURATA MANUFACTURING CO LTD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+9.93%5700</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+9.93%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.79%134,000</t>
+          <t>1.89%418,400</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.89%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>134000</v>
+        <v>418400</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:09</t>
+          <t>2026-10-06 19:17:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6920LASERTEC CORP</t>
+          <t>4062IBIDEN CO LTD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -965,16 +965,16 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.50%62,100</t>
+          <t>1.49%236,200</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>62100</v>
+        <v>236200</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:09</t>
+          <t>2026-10-06 19:17:16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4062IBIDEN CO LTD</t>
+          <t>6920LASERTEC CORP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1028,16 +1028,16 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.49%236,200</t>
+          <t>1.48%62,100</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>236200</v>
+        <v>62100</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:10</t>
+          <t>2026-10-06 19:17:16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+4.22%3585</t>
+          <t>+2.79%3685</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+4.22%</t>
+          <t>+2.79%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3585</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.40%158,000</t>
+          <t>1.45%158,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:10</t>
+          <t>2026-10-06 19:17:16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1139,27 +1139,27 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+2.4%1495</t>
+          <t>+0.67%1505</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.31%348,000</t>
+          <t>1.33%348,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.33%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:10</t>
+          <t>2026-10-06 19:17:18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,27 +1202,27 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.51%294</t>
+          <t>+1.36%298</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>298</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.27%1,665,000</t>
+          <t>1.25%1,665,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:10</t>
+          <t>2026-10-06 19:17:18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,27 +1265,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+5.6%2075</t>
+          <t>-1.2%2050</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+5.6%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.98%193,000</t>
+          <t>1.03%193,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>1.03%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:10</t>
+          <t>2026-10-06 19:17:18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,27 +1328,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+6.16%2325</t>
+          <t>+1.08%2350</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+6.16%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.74%130,000</t>
+          <t>0.77%130,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:10</t>
+          <t>2026-10-06 19:17:18</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.70%7,234</t>
+          <t>0.69%7,234</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.69%</t>
         </is>
       </c>
       <c r="K16" t="n">

--- a/etf_holdings/2026-10-06_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:15</t>
+          <t>2026-10-06 23:19:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:15</t>
+          <t>2026-10-06 23:19:47</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:15</t>
+          <t>2026-10-06 23:19:47</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:15</t>
+          <t>2026-10-06 23:19:47</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:16</t>
+          <t>2026-10-06 23:19:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:16</t>
+          <t>2026-10-06 23:19:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:16</t>
+          <t>2026-10-06 23:19:48</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:16</t>
+          <t>2026-10-06 23:19:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:16</t>
+          <t>2026-10-06 23:19:48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:16</t>
+          <t>2026-10-06 23:19:48</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:16</t>
+          <t>2026-10-06 23:19:48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:18</t>
+          <t>2026-10-06 23:19:50</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:18</t>
+          <t>2026-10-06 23:19:50</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:18</t>
+          <t>2026-10-06 23:19:50</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:18</t>
+          <t>2026-10-06 23:19:50</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/etf_holdings/2026-10-06_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:47</t>
+          <t>2026-10-06 23:28:17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:47</t>
+          <t>2026-10-06 23:28:17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:47</t>
+          <t>2026-10-06 23:28:17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:47</t>
+          <t>2026-10-06 23:28:17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:48</t>
+          <t>2026-10-06 23:28:18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:48</t>
+          <t>2026-10-06 23:28:18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:48</t>
+          <t>2026-10-06 23:28:18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:48</t>
+          <t>2026-10-06 23:28:18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:48</t>
+          <t>2026-10-06 23:28:18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:48</t>
+          <t>2026-10-06 23:28:18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:48</t>
+          <t>2026-10-06 23:28:18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:50</t>
+          <t>2026-10-06 23:28:20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:50</t>
+          <t>2026-10-06 23:28:20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:50</t>
+          <t>2026-10-06 23:28:20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:50</t>
+          <t>2026-10-06 23:28:20</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/etf_holdings/2026-10-06_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:17</t>
+          <t>2026-10-06 23:58:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:17</t>
+          <t>2026-10-06 23:58:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:17</t>
+          <t>2026-10-06 23:58:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:17</t>
+          <t>2026-10-06 23:58:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:18</t>
+          <t>2026-10-06 23:58:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:18</t>
+          <t>2026-10-06 23:58:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:18</t>
+          <t>2026-10-06 23:58:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:18</t>
+          <t>2026-10-06 23:58:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:18</t>
+          <t>2026-10-06 23:58:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:18</t>
+          <t>2026-10-06 23:58:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:18</t>
+          <t>2026-10-06 23:58:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:20</t>
+          <t>2026-10-06 23:58:54</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:20</t>
+          <t>2026-10-06 23:58:54</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:20</t>
+          <t>2026-10-06 23:58:54</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:20</t>
+          <t>2026-10-06 23:58:54</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
